--- a/PromVesClient/Templates/CardTemplate.xlsx
+++ b/PromVesClient/Templates/CardTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Клиент\PromVesClient\PromVesClient\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DCB6EE-8916-4309-BD39-8F8981C0D674}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F281B9-BE45-4E8C-8A74-CF7B4D71DE8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Номер вагона</t>
   </si>
@@ -61,13 +61,16 @@
   </si>
   <si>
     <t>Недогруз перегруз, т.</t>
+  </si>
+  <si>
+    <t>АО «Уральский завод металлоконструкций»</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +87,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -93,7 +104,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -108,9 +119,16 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
-      </top>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -120,10 +138,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -405,13 +429,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
     <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" customWidth="1"/>
     <col min="7" max="7" width="9.5703125" customWidth="1"/>
@@ -422,45 +446,64 @@
     <col min="12" max="12" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/PromVesClient/Templates/CardTemplate.xlsx
+++ b/PromVesClient/Templates/CardTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Клиент\PromVesClient\PromVesClient\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F281B9-BE45-4E8C-8A74-CF7B4D71DE8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E892DDC-73A8-43E5-8867-763974A9883D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,9 +39,6 @@
     <t>Брутто, т.</t>
   </si>
   <si>
-    <t>Грузоподьемность, т.</t>
-  </si>
-  <si>
     <t>Разница бортов, т.</t>
   </si>
   <si>
@@ -64,6 +61,9 @@
   </si>
   <si>
     <t>АО «Уральский завод металлоконструкций»</t>
+  </si>
+  <si>
+    <t>Грузоподъёмность, т.</t>
   </si>
 </sst>
 </file>
@@ -439,7 +439,7 @@
     <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" customWidth="1"/>
     <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" customWidth="1"/>
     <col min="10" max="10" width="9.28515625" customWidth="1"/>
     <col min="11" max="11" width="10.28515625" customWidth="1"/>
@@ -448,7 +448,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -476,28 +476,28 @@
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
